--- a/Result/profitability/6498.xlsx
+++ b/Result/profitability/6498.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4625,6 +4625,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6498</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>379</v>
+      </c>
+      <c r="D34" t="n">
+        <v>212</v>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>44</v>
+      </c>
+      <c r="G34" t="n">
+        <v>109</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>28.90%</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>118</v>
+      </c>
+      <c r="K34" t="n">
+        <v>87</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.7575</v>
+      </c>
+      <c r="N34" t="n">
+        <v>47.35625</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.05714285714285716</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>-1.710000000000001</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-0.03740975716473416</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.9072164948453609</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>-3.439999999999998</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>-0.07251264755480602</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
